--- a/data/trans_orig/IP15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP15-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37251</t>
+          <t>37815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48341</t>
+          <t>46930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70347</t>
+          <t>69123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69355</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83749</t>
+          <t>83863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84129</t>
+          <t>83565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>98822</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157204</t>
+          <t>158428</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179210</t>
+          <t>180621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54365</t>
+          <t>52629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41367</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61874</t>
+          <t>62228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81443</t>
+          <t>81157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109345</t>
+          <t>109185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198840</t>
+          <t>200576</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>218418</t>
+          <t>219041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191882</t>
+          <t>191528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212389</t>
+          <t>211984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397616</t>
+          <t>397776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425518</t>
+          <t>425804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30190</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31296</t>
+          <t>31558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>37436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>57088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97358</t>
+          <t>96535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111450</t>
+          <t>110999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110219</t>
+          <t>109957</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125238</t>
+          <t>123961</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211626</t>
+          <t>211975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232288</t>
+          <t>231627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22509</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39077</t>
+          <t>38596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>30869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49537</t>
+          <t>49153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56226</t>
+          <t>59193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81399</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155020</t>
+          <t>155501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171588</t>
+          <t>171346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156512</t>
+          <t>156896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175073</t>
+          <t>175180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318747</t>
+          <t>316535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343920</t>
+          <t>340953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110980</t>
+          <t>110452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142532</t>
+          <t>142934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>127498</t>
+          <t>127646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161419</t>
+          <t>162371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245290</t>
+          <t>246620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292494</t>
+          <t>293691</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538489</t>
+          <t>538087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>570041</t>
+          <t>570569</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>561281</t>
+          <t>560329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>595202</t>
+          <t>595054</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1111227</t>
+          <t>1110030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1158431</t>
+          <t>1157101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>28310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44621</t>
+          <t>45973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30224</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48358</t>
+          <t>48705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63989</t>
+          <t>61769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88398</t>
+          <t>86717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102140</t>
+          <t>100788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118642</t>
+          <t>118451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97632</t>
+          <t>97285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>115766</t>
+          <t>116278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204353</t>
+          <t>206034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228762</t>
+          <t>230982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43694</t>
+          <t>43749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65161</t>
+          <t>65646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55708</t>
+          <t>55951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79189</t>
+          <t>79910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105398</t>
+          <t>106516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137787</t>
+          <t>137901</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171089</t>
+          <t>170604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192556</t>
+          <t>192501</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189802</t>
+          <t>189081</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213283</t>
+          <t>213040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>367454</t>
+          <t>367340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399843</t>
+          <t>398725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38291</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20678</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>46910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70175</t>
+          <t>69952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118752</t>
+          <t>118240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134910</t>
+          <t>134515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121284</t>
+          <t>121433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137115</t>
+          <t>137810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244661</t>
+          <t>244884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267390</t>
+          <t>267926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>35529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18302</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>32342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42653</t>
+          <t>41737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64645</t>
+          <t>64387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135507</t>
+          <t>135808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151527</t>
+          <t>150671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146151</t>
+          <t>146891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160931</t>
+          <t>161573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>286183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307917</t>
+          <t>308833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130280</t>
+          <t>130633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>167322</t>
+          <t>166963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140344</t>
+          <t>140740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177591</t>
+          <t>177977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>281654</t>
+          <t>279624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>332147</t>
+          <t>331255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544069</t>
+          <t>544428</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>581111</t>
+          <t>580758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>574417</t>
+          <t>574031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>611664</t>
+          <t>611268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1131252</t>
+          <t>1132144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1181745</t>
+          <t>1183775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34806</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>32286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40945</t>
+          <t>41383</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61205</t>
+          <t>60384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96848</t>
+          <t>96367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>111286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93378</t>
+          <t>91878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106461</t>
+          <t>106763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>194613</t>
+          <t>195434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214873</t>
+          <t>214435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33585</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52399</t>
+          <t>52131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32558</t>
+          <t>33485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73626</t>
+          <t>72210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100177</t>
+          <t>99177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158118</t>
+          <t>158386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176932</t>
+          <t>177000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>204841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225503</t>
+          <t>224576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368401</t>
+          <t>369401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394952</t>
+          <t>396368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45783</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41972</t>
+          <t>41868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>57797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83689</t>
+          <t>81412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143116</t>
+          <t>143393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160865</t>
+          <t>161508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146600</t>
+          <t>146704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163654</t>
+          <t>163430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293782</t>
+          <t>296059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319788</t>
+          <t>319674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31072</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>34362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56724</t>
+          <t>54721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>143537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158728</t>
+          <t>157828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142976</t>
+          <t>143071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158386</t>
+          <t>157529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290624</t>
+          <t>292627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>311939</t>
+          <t>312986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111129</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144884</t>
+          <t>143709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107274</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142274</t>
+          <t>141931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228851</t>
+          <t>227717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273319</t>
+          <t>273513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>559487</t>
+          <t>560662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>593242</t>
+          <t>593128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>602570</t>
+          <t>602913</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>637570</t>
+          <t>636759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175896</t>
+          <t>1175702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220364</t>
+          <t>1221498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30954</t>
+          <t>30254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>45579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36064</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46273</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33049</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44560</t>
+          <t>44365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>73376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88001</t>
+          <t>88701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>58238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39208</t>
+          <t>39473</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60254</t>
+          <t>60692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81524</t>
+          <t>82400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110528</t>
+          <t>110349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102327</t>
+          <t>101061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122321</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121593</t>
+          <t>121155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142639</t>
+          <t>142374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>230619</t>
+          <t>230798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259623</t>
+          <t>258747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28666</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46624</t>
+          <t>46699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>35438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58658</t>
+          <t>58380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69766</t>
+          <t>69693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100122</t>
+          <t>97982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122949</t>
+          <t>122874</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140907</t>
+          <t>140634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153832</t>
+          <t>154110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176104</t>
+          <t>177052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281941</t>
+          <t>284081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>312297</t>
+          <t>312370</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>134435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50104</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>80893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113758</t>
+          <t>112737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210703</t>
+          <t>220506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142209</t>
+          <t>141023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224021</t>
+          <t>223345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225155</t>
+          <t>224590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255379</t>
+          <t>254923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370237</t>
+          <t>360434</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>467182</t>
+          <t>468203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148523</t>
+          <t>147455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>256457</t>
+          <t>245221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162543</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206332</t>
+          <t>206571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323800</t>
+          <t>324265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>435188</t>
+          <t>426090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405384</t>
+          <t>416620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>513318</t>
+          <t>514386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554933</t>
+          <t>554694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>598722</t>
+          <t>601233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>987918</t>
+          <t>997016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1099306</t>
+          <t>1098841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP15-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22688</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38163</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22308</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37271</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21766</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36311</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>27,35%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37815</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46930</t>
+          <t>49894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69123</t>
+          <t>70402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>91725</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83217</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>98692</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>77136</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68900</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83863</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69860</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>84405</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>72,65%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>91725</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>83565</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>98822</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>75,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158428</t>
+          <t>157149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180621</t>
+          <t>177657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41380</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>63124</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>34164</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>52629</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>33921</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>53266</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,07%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,78%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>41772</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>62228</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81157</t>
+          <t>80974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109185</t>
+          <t>109873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202796</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>190632</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212376</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>313</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>209984</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200576</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>219041</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>199939</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>219284</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>202796</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>191528</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>211984</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>79,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397776</t>
+          <t>397088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425804</t>
+          <t>425987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16676</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31049</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16549</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31013</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16466</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30278</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>17554</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>31558</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37436</t>
+          <t>37042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57088</t>
+          <t>56869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117649</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>110466</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>124839</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>105041</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>96535</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>110999</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>97270</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>111082</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,35%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>117649</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>109957</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>123961</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211975</t>
+          <t>212194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231627</t>
+          <t>232021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30481</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22751</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38596</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23146</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39674</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,74%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30869</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>49153</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59193</t>
+          <t>58847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83611</t>
+          <t>83544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166611</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>157049</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>175568</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>163554</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>155501</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>171346</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>154423</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>170951</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>166611</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>156896</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>175180</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316535</t>
+          <t>316602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340953</t>
+          <t>341299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,107 +2095,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>127434</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>163024</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>110452</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>142934</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>109450</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>141613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>127646</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>162371</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>16,07%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>269224</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>247844</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>292802</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>17,66%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>269224</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>246620</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>293691</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2208,107 +2208,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>578781</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>559676</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>595266</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>828</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>555716</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>538087</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>570569</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>539408</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>571571</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>81,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>578781</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>560329</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>595054</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>83,93%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1699</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1134497</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1110919</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1155877</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>80,82%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>79,14%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>82,34%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1699</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1134497</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1110030</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1157101</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>80,82%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>79,08%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30299</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47601</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>36498</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28310</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45973</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28930</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>44806</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29712</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48705</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,32%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61769</t>
+          <t>62042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86717</t>
+          <t>87373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>107564</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98389</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>115691</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>73,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>110263</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100788</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>118451</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101955</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>117831</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>107564</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>97285</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>116278</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>73,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206034</t>
+          <t>205378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>230982</t>
+          <t>230709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56106</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79414</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54165</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43749</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>65646</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42842</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>65626</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>22,93%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>55951</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>79910</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>25,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106516</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>139235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>201626</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>189577</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212885</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>74,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>182085</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170604</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>192501</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>170624</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>193408</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,07%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>201626</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>189081</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>213040</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>74,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>367340</t>
+          <t>366006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398725</t>
+          <t>398730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20687</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36845</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22528</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38803</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22518</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>38503</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>14,34%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19983</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>36360</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46910</t>
+          <t>47507</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69952</t>
+          <t>69378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>129878</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120948</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>137106</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127173</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>118240</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134515</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>118540</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>134525</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>85,66%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>129878</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>121433</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>137810</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>82,31%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>76,96%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>87,34%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>369</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244884</t>
+          <t>245458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267926</t>
+          <t>267329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157793</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157793</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157793</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157793</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157793</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157793</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18393</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33770</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20666</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35529</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20017</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35892</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>17660</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32342</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41737</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64387</t>
+          <t>62972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>154365</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>145463</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>160840</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>144168</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>135808</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>150671</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>135445</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>151320</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>154365</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>146891</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>161573</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,13%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286183</t>
+          <t>287598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308833</t>
+          <t>309117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179233</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179233</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179233</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179233</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179233</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>139830</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>176392</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>130633</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>166963</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>129929</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>165279</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>140740</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>177977</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>279624</t>
+          <t>280503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>331255</t>
+          <t>332508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>593434</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>575616</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>612178</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>78,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>81,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>812</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>563690</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>544428</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>580758</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>546112</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>581462</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>849</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>593434</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>574031</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>611268</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1132144</t>
+          <t>1130891</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1183775</t>
+          <t>1182896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17475</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31789</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20368</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35287</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20289</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34909</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17401</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32286</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>41200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60384</t>
+          <t>62463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>100188</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>92375</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>106689</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104621</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>96367</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>111286</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>96745</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>111365</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>79,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>100188</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>91878</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>106763</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195434</t>
+          <t>193355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214435</t>
+          <t>214618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33879</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53046</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33517</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>52131</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>33605</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>52224</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,06%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>33485</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>53220</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72210</t>
+          <t>72720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99177</t>
+          <t>100088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>214965</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>205015</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224182</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>168278</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>158386</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>177000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>158293</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>176912</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>214965</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>204841</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>224576</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369401</t>
+          <t>368490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396368</t>
+          <t>395858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24733</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42651</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27391</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45506</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27504</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45794</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>25142</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41868</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57797</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81412</t>
+          <t>83847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155126</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145921</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>163839</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152775</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143393</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161508</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>143105</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>161395</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>155126</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>146704</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>163430</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>296059</t>
+          <t>293624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319674</t>
+          <t>318313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16449</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31792</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15473</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29764</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15258</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30679</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16519</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30977</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34362</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54721</t>
+          <t>56398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>151290</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>142256</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>157599</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>151236</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>143537</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>157828</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>142622</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>158043</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>151290</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>143071</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>157529</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292627</t>
+          <t>290950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312986</t>
+          <t>312355</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>106791</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140198</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>111243</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>143709</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>110759</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>144834</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>108085</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>141931</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227717</t>
+          <t>226261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273513</t>
+          <t>274110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>621568</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>604646</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>638053</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>869</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>576910</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>560662</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>593128</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>559537</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>593612</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>81,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>621568</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>602913</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>636759</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175702</t>
+          <t>1175105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1221498</t>
+          <t>1222954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17432</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13281</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22565</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11138</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21341</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30254</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45579</t>
+          <t>38417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33105</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27972</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37256</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41528</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36170</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46373</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>72,21%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33086</t>
+          <t>32723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44365</t>
+          <t>41978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>80615</t>
+          <t>71026</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73376</t>
+          <t>64210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88701</t>
+          <t>77829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32476</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50656</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38176</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>58238</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39473</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60692</t>
+          <t>49823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82400</t>
+          <t>69642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110349</t>
+          <t>93829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>115670</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>106249</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>124429</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>112676</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101061</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>121123</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>132863</t>
+          <t>104622</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121155</t>
+          <t>95695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142374</t>
+          <t>112379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>245540</t>
+          <t>220292</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>230798</t>
+          <t>208594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>258747</t>
+          <t>232781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,107 +7250,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33470</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54230</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28939</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46699</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>37948</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>29276</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>48258</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>81919</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>68525</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>96183</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>21,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>46169</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>35438</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58380</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>83320</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>69693</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>97982</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -7363,107 +7363,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156155</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145896</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166656</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,03%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>132422</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>122874</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>140634</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>135858</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>125548</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>144530</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>72,23%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>83,16%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>292012</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>277748</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>305406</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>78,09%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166321</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154110</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>177052</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>72,53%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>83,32%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>298743</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>284081</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>312370</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>78,19%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>169573</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>169573</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>169573</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173806</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>382063</t>
+          <t>373931</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>382063</t>
+          <t>373931</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>382063</t>
+          <t>373931</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49495</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80058</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>52113</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>134435</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>48,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50560</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80893</t>
+          <t>63958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112737</t>
+          <t>94233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220506</t>
+          <t>132031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>230332</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>212587</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>243150</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>197501</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>141023</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>223345</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>240791</t>
+          <t>206573</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224590</t>
+          <t>192595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>254923</t>
+          <t>216636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>438291</t>
+          <t>436905</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360434</t>
+          <t>417167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>468203</t>
+          <t>454965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>143688</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>185319</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>147455</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>245221</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160032</t>
+          <t>125557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206571</t>
+          <t>161697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>324265</t>
+          <t>282577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>426090</t>
+          <t>337946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>535261</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>514894</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>556525</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>715</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>484126</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>416620</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>514386</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>62,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>77,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>579064</t>
+          <t>484974</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554694</t>
+          <t>466269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>601233</t>
+          <t>502409</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1063190</t>
+          <t>1020235</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>997016</t>
+          <t>990233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1098841</t>
+          <t>1045602</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>661841</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>661841</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>661841</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627966</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1423106</t>
+          <t>1328179</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1423106</t>
+          <t>1328179</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1423106</t>
+          <t>1328179</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
